--- a/paper_final_tables/tab4_1_uav_main_results.xlsx
+++ b/paper_final_tables/tab4_1_uav_main_results.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="138">
   <si>
     <t>Scene</t>
   </si>
@@ -175,6 +175,258 @@
   </si>
   <si>
     <t>1.0000</t>
+  </si>
+  <si>
+    <t>Scene</t>
+  </si>
+  <si>
+    <t>Scene 1</t>
+  </si>
+  <si>
+    <t>Scene 2</t>
+  </si>
+  <si>
+    <t>Scene 4</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Statistic</t>
+  </si>
+  <si>
+    <t>Mean ± Std</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Mean ± Std</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Mean ± Std</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>PSO</t>
+  </si>
+  <si>
+    <t>GWO</t>
+  </si>
+  <si>
+    <t>HHO</t>
+  </si>
+  <si>
+    <t>WOA</t>
+  </si>
+  <si>
+    <t>FAEAE</t>
+  </si>
+  <si>
+    <t>305.1007 ± 0.7213</t>
+  </si>
+  <si>
+    <t>1.0000</t>
+  </si>
+  <si>
+    <t>316.4880 ± 3.9907</t>
+  </si>
+  <si>
+    <t>1.0000</t>
+  </si>
+  <si>
+    <t>326.3252 ± 6.7014</t>
+  </si>
+  <si>
+    <t>1.0000</t>
+  </si>
+  <si>
+    <t>Scene</t>
+  </si>
+  <si>
+    <t>Scene 1</t>
+  </si>
+  <si>
+    <t>Scene 2</t>
+  </si>
+  <si>
+    <t>Scene 4</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Statistic</t>
+  </si>
+  <si>
+    <t>Mean ± Std</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Mean ± Std</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Mean ± Std</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>291.3828 ± 3.4281</t>
+  </si>
+  <si>
+    <t>2.0000</t>
+  </si>
+  <si>
+    <t>1299.2323 ± 1204.0216</t>
+  </si>
+  <si>
+    <t>6.0000</t>
+  </si>
+  <si>
+    <t>2153.8246 ± 630.0714</t>
+  </si>
+  <si>
+    <t>6.0000</t>
+  </si>
+  <si>
+    <t>4.6667</t>
+  </si>
+  <si>
+    <t>PSO</t>
+  </si>
+  <si>
+    <t>285.4583 ± 10.4708</t>
+  </si>
+  <si>
+    <t>1.0000</t>
+  </si>
+  <si>
+    <t>664.4080 ± 473.5398</t>
+  </si>
+  <si>
+    <t>4.0000</t>
+  </si>
+  <si>
+    <t>1129.4685 ± 445.5469</t>
+  </si>
+  <si>
+    <t>4.0000</t>
+  </si>
+  <si>
+    <t>3.0000</t>
+  </si>
+  <si>
+    <t>GWO</t>
+  </si>
+  <si>
+    <t>332.5641 ± 21.0008</t>
+  </si>
+  <si>
+    <t>5.0000</t>
+  </si>
+  <si>
+    <t>332.5819 ± 21.9407</t>
+  </si>
+  <si>
+    <t>2.0000</t>
+  </si>
+  <si>
+    <t>526.5065 ± 250.0036</t>
+  </si>
+  <si>
+    <t>2.0000</t>
+  </si>
+  <si>
+    <t>3.0000</t>
+  </si>
+  <si>
+    <t>HHO</t>
+  </si>
+  <si>
+    <t>310.9784 ± 67.6982</t>
+  </si>
+  <si>
+    <t>4.0000</t>
+  </si>
+  <si>
+    <t>394.0178 ± 229.3555</t>
+  </si>
+  <si>
+    <t>3.0000</t>
+  </si>
+  <si>
+    <t>925.7374 ± 409.7295</t>
+  </si>
+  <si>
+    <t>3.0000</t>
+  </si>
+  <si>
+    <t>3.3333</t>
+  </si>
+  <si>
+    <t>WOA</t>
+  </si>
+  <si>
+    <t>334.5945 ± 122.5534</t>
+  </si>
+  <si>
+    <t>6.0000</t>
+  </si>
+  <si>
+    <t>779.6635 ± 651.7707</t>
+  </si>
+  <si>
+    <t>5.0000</t>
+  </si>
+  <si>
+    <t>1486.2090 ± 453.8427</t>
+  </si>
+  <si>
+    <t>5.0000</t>
+  </si>
+  <si>
+    <t>5.3333</t>
+  </si>
+  <si>
+    <t>FAEAE</t>
+  </si>
+  <si>
+    <t>302.3221 ± 0.9123</t>
+  </si>
+  <si>
+    <t>3.0000</t>
+  </si>
+  <si>
+    <t>321.0269 ± 6.7946</t>
+  </si>
+  <si>
+    <t>1.0000</t>
+  </si>
+  <si>
+    <t>330.4251 ± 2.3383</t>
+  </si>
+  <si>
+    <t>1.0000</t>
+  </si>
+  <si>
+    <t>1.6667</t>
   </si>
 </sst>
 </file>
@@ -225,220 +477,220 @@
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
     <col min="2" max="2" width="10.85546875" customWidth="true"/>
-    <col min="3" max="3" width="19.140625" customWidth="true"/>
+    <col min="3" max="3" width="20.140625" customWidth="true"/>
     <col min="4" max="4" width="19.140625" customWidth="true"/>
     <col min="5" max="5" width="18.140625" customWidth="true"/>
     <col min="6" max="6" width="18.140625" customWidth="true"/>
     <col min="7" max="7" width="19.140625" customWidth="true"/>
-    <col min="8" max="8" width="17.140625" customWidth="true"/>
+    <col min="8" max="8" width="16.140625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>33</v>
+        <v>114</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>47</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>51</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>52</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>39</v>
+        <v>120</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>46</v>
+        <v>129</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
